--- a/Lab-04/report.xlsx
+++ b/Lab-04/report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>Story ID</t>
   </si>
@@ -19,7 +19,7 @@
     <t>Story Name</t>
   </si>
   <si>
-    <t>Ali Est</t>
+    <t>AI Est</t>
   </si>
   <si>
     <t>Member 2 Est</t>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t>Team Agreed Est</t>
-  </si>
-  <si>
-    <t>AI Est</t>
   </si>
   <si>
     <t>Difference</t>
@@ -497,7 +494,14 @@
   <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="26" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="13.571428571428571" customWidth="1"/>
+    <col min="2" max="2" width="44.285714285714285" customWidth="1"/>
+    <col min="3" max="3" width="13.571428571428571" customWidth="1"/>
+    <col min="4" max="4" width="18.285714285714285" customWidth="1"/>
+    <col min="5" max="6" width="18.571428571428573" customWidth="1"/>
+    <col min="7" max="8" width="13.571428571428571" customWidth="1"/>
+    <col min="9" max="9" width="85.57142857142857" customWidth="1"/>
+    <col min="10" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -520,13 +524,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -534,7 +538,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1">
         <v>3</v>
@@ -555,7 +559,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -563,7 +567,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -584,7 +588,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -592,7 +596,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -613,7 +617,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -621,28 +625,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1">
+        <v>5</v>
+      </c>
+      <c r="H5" s="1">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C5" s="1">
-        <v>5</v>
-      </c>
-      <c r="D5" s="1">
-        <v>8</v>
-      </c>
-      <c r="E5" s="1">
-        <v>8</v>
-      </c>
-      <c r="F5" s="1">
-        <v>8</v>
-      </c>
-      <c r="G5" s="1">
-        <v>5</v>
-      </c>
-      <c r="H5" s="1">
-        <v>3</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -650,7 +654,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -671,7 +675,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -679,28 +683,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1">
+        <v>5</v>
+      </c>
+      <c r="F7" s="1">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C7" s="1">
-        <v>5</v>
-      </c>
-      <c r="D7" s="1">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1">
-        <v>5</v>
-      </c>
-      <c r="F7" s="1">
-        <v>5</v>
-      </c>
-      <c r="G7" s="1">
-        <v>3</v>
-      </c>
-      <c r="H7" s="1">
-        <v>2</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -708,7 +712,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1">
         <v>8</v>
@@ -729,7 +733,7 @@
         <v>-5</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -737,7 +741,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
@@ -758,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -766,7 +770,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
@@ -787,7 +791,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -795,7 +799,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1">
         <v>5</v>
@@ -816,7 +820,7 @@
         <v>-3</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
